--- a/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Butterflies/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Butterflies/heatmap.xlsx
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
